--- a/results/MCMC models.xlsx
+++ b/results/MCMC models.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="606" documentId="8_{DB5915DE-6E39-4037-8B18-600C761C23FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97354356-7BEA-43A8-B456-0782A4F3F336}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B49123BC-4E6F-40A9-8952-79BC4B1B8C9F}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B49123BC-4E6F-40A9-8952-79BC4B1B8C9F}"/>
   </bookViews>
   <sheets>
     <sheet name="MCMC_coldstrat" sheetId="1" r:id="rId1"/>
@@ -189,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -201,9 +201,6 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -595,7 +592,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B5">
@@ -615,7 +612,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B6">
@@ -790,7 +787,7 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B6">
@@ -808,7 +805,7 @@
       <c r="F6">
         <v>0.30443999999999999</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="I6">
@@ -828,7 +825,7 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B7">
@@ -849,7 +846,7 @@
       <c r="G7" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="1" t="s">
         <v>26</v>
       </c>
       <c r="I7">
@@ -869,7 +866,7 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B8">
@@ -1067,7 +1064,7 @@
       </c>
     </row>
     <row r="20" spans="8:13" x14ac:dyDescent="0.25">
-      <c r="H20" s="6" t="s">
+      <c r="H20" s="1" t="s">
         <v>11</v>
       </c>
       <c r="I20">
@@ -1087,7 +1084,7 @@
       </c>
     </row>
     <row r="21" spans="8:13" x14ac:dyDescent="0.25">
-      <c r="H21" s="6" t="s">
+      <c r="H21" s="1" t="s">
         <v>26</v>
       </c>
       <c r="I21">
@@ -1215,7 +1212,7 @@
       </c>
     </row>
     <row r="34" spans="8:13" x14ac:dyDescent="0.25">
-      <c r="H34" s="6" t="s">
+      <c r="H34" s="1" t="s">
         <v>11</v>
       </c>
       <c r="I34">
@@ -1235,7 +1232,7 @@
       </c>
     </row>
     <row r="35" spans="8:13" x14ac:dyDescent="0.25">
-      <c r="H35" s="6" t="s">
+      <c r="H35" s="1" t="s">
         <v>26</v>
       </c>
       <c r="I35">
@@ -1273,7 +1270,7 @@
       <c r="H38" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I38" s="6">
+      <c r="I38" s="1">
         <v>2.8260000000000001</v>
       </c>
       <c r="J38" s="3">
@@ -1290,7 +1287,7 @@
       <c r="H39" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I39" s="6">
+      <c r="I39" s="1">
         <v>10.1</v>
       </c>
       <c r="J39" s="3">
@@ -1376,7 +1373,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B6">
@@ -1396,7 +1393,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B7">
@@ -1525,7 +1522,7 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B19">
@@ -1548,7 +1545,7 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B20">

--- a/results/MCMC models.xlsx
+++ b/results/MCMC models.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioviedo-my.sharepoint.com/personal/espinosaclara_uniovi_es/Documents/IMIB/Softwares/GitHub/Germination_drivers/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="606" documentId="8_{DB5915DE-6E39-4037-8B18-600C761C23FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97354356-7BEA-43A8-B456-0782A4F3F336}"/>
+  <xr:revisionPtr revIDLastSave="639" documentId="8_{DB5915DE-6E39-4037-8B18-600C761C23FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB3CB372-2CC7-4BB2-B3AB-B540E6925833}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B49123BC-4E6F-40A9-8952-79BC4B1B8C9F}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="2" xr2:uid="{B49123BC-4E6F-40A9-8952-79BC4B1B8C9F}"/>
   </bookViews>
   <sheets>
     <sheet name="MCMC_coldstrat" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="38">
   <si>
     <t>post.mean</t>
   </si>
@@ -139,10 +139,19 @@
     <t>germination in constant temp ~ community</t>
   </si>
   <si>
+    <t>very much left skewed</t>
+  </si>
+  <si>
+    <t>germ_reduction ~ community (exponential?)</t>
+  </si>
+  <si>
+    <t>need to make mean value per species to avoid negative</t>
+  </si>
+  <si>
     <t>germ_reduction ~ community (gaussian?)</t>
   </si>
   <si>
-    <t>very much left skewed</t>
+    <t>diagnostics plots look okei</t>
   </si>
 </sst>
 </file>
@@ -189,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -201,6 +210,9 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1333,28 +1345,29 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ACA2A48-20E5-450E-985C-69700C004D4F}">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.5703125" customWidth="1"/>
+    <col min="9" max="9" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" t="s">
         <v>0</v>
@@ -1372,7 +1385,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -1392,7 +1405,7 @@
         <v>0.85899999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -1415,7 +1428,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" t="s">
         <v>0</v>
@@ -1430,7 +1443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>2</v>
       </c>
@@ -1447,7 +1460,7 @@
         <v>1709</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>3</v>
       </c>
@@ -1464,7 +1477,7 @@
         <v>2176</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" t="s">
         <v>7</v>
@@ -1476,7 +1489,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
@@ -1490,20 +1503,35 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" t="s">
         <v>33</v>
       </c>
-      <c r="C15" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I15" t="s">
+        <v>36</v>
+      </c>
+      <c r="K15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" t="s">
+        <v>20</v>
+      </c>
+      <c r="K16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" t="s">
         <v>0</v>
@@ -1520,22 +1548,38 @@
       <c r="F18" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I18" s="1"/>
+      <c r="J18" t="s">
+        <v>0</v>
+      </c>
+      <c r="K18" t="s">
+        <v>4</v>
+      </c>
+      <c r="L18" t="s">
+        <v>5</v>
+      </c>
+      <c r="M18" t="s">
+        <v>1</v>
+      </c>
+      <c r="N18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B19">
-        <v>67.451999999999998</v>
+        <v>-4.2588999999999997</v>
       </c>
       <c r="C19">
-        <v>44.62</v>
+        <v>-4.9219999999999997</v>
       </c>
       <c r="D19">
-        <v>89.606999999999999</v>
+        <v>-3.6705999999999999</v>
       </c>
       <c r="E19">
-        <v>9000</v>
+        <v>8868</v>
       </c>
       <c r="F19" t="s">
         <v>19</v>
@@ -1543,28 +1587,67 @@
       <c r="G19" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I19" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="J19">
+        <v>66.400000000000006</v>
+      </c>
+      <c r="K19">
+        <v>42.692</v>
+      </c>
+      <c r="L19">
+        <v>89.185000000000002</v>
+      </c>
+      <c r="M19">
+        <v>8212</v>
+      </c>
+      <c r="N19" t="s">
+        <v>19</v>
+      </c>
+      <c r="O19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B20">
-        <v>6.9480000000000004</v>
+        <v>-0.13220000000000001</v>
       </c>
       <c r="C20">
-        <v>-12.154999999999999</v>
+        <v>-0.92279999999999995</v>
       </c>
       <c r="D20">
-        <v>25.645</v>
+        <v>0.64429999999999998</v>
       </c>
       <c r="E20">
-        <v>9000</v>
+        <v>9017</v>
       </c>
       <c r="F20">
-        <v>0.45400000000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.73099999999999998</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J20">
+        <v>9.0050000000000008</v>
+      </c>
+      <c r="K20">
+        <v>-9.6170000000000009</v>
+      </c>
+      <c r="L20">
+        <v>28.312999999999999</v>
+      </c>
+      <c r="M20">
+        <v>8099</v>
+      </c>
+      <c r="N20">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" t="s">
         <v>0</v>
@@ -1578,42 +1661,85 @@
       <c r="E22" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I22" s="1"/>
+      <c r="J22" t="s">
+        <v>0</v>
+      </c>
+      <c r="K22" t="s">
+        <v>4</v>
+      </c>
+      <c r="L22" t="s">
+        <v>5</v>
+      </c>
+      <c r="M22" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B23" s="1">
-        <v>463.6</v>
+        <v>9.0020000000000003E-2</v>
       </c>
       <c r="C23" s="3">
-        <v>4.1690000000000002E-6</v>
+        <v>3.557E-11</v>
       </c>
       <c r="D23" s="3">
-        <v>1596</v>
+        <v>0.36049999999999999</v>
       </c>
       <c r="E23">
-        <v>9400</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+        <v>8717</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J23" s="1">
+        <v>518.4</v>
+      </c>
+      <c r="K23" s="3">
+        <v>5.344E-6</v>
+      </c>
+      <c r="L23" s="3">
+        <v>1685</v>
+      </c>
+      <c r="M23">
+        <v>8161</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B24" s="1">
-        <v>592.79999999999995</v>
+        <v>5.7239999999999999E-2</v>
       </c>
       <c r="C24" s="3">
-        <v>3.9750000000000001E-4</v>
+        <v>1.177E-9</v>
       </c>
       <c r="D24" s="3">
-        <v>1137</v>
+        <v>0.2218</v>
       </c>
       <c r="E24">
-        <v>8567</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+        <v>9000</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="1">
+        <v>489.2</v>
+      </c>
+      <c r="K24" s="3">
+        <v>7.2479999999999997E-5</v>
+      </c>
+      <c r="L24" s="3">
+        <v>1063</v>
+      </c>
+      <c r="M24">
+        <v>8340</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" t="s">
         <v>7</v>
@@ -1624,23 +1750,46 @@
       <c r="D25" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I25" s="1"/>
+      <c r="J25" t="s">
+        <v>7</v>
+      </c>
+      <c r="K25" t="s">
+        <v>8</v>
+      </c>
+      <c r="L25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B26">
-        <v>0.37</v>
+        <v>0.32</v>
       </c>
       <c r="C26" s="4">
         <v>0</v>
       </c>
       <c r="D26">
-        <v>0.77</v>
+        <v>0.82</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K26" s="4"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
